--- a/Archivio/Setup/Progress_Descrizione.xlsx
+++ b/Archivio/Setup/Progress_Descrizione.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TestDb\PvPmo\Archivio\Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80619441-BD4A-43C8-A474-6219DCD53524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C0CC80-642F-408C-9109-0904EECA380E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B90D8C67-B101-43D7-B3A6-F48ADA6E1AB3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="45">
   <si>
     <t>TabellaSql</t>
   </si>
@@ -77,18 +77,6 @@
     <t>Caricamento file impostazioni.</t>
   </si>
   <si>
-    <t>Aggiornamento mensile approvazione Timesheet.</t>
-  </si>
-  <si>
-    <t>Aggiornamento mensile RES10.</t>
-  </si>
-  <si>
-    <t>Aggiornamento mensile ore lavorate X work.</t>
-  </si>
-  <si>
-    <t>Aggiornamento mensile progetti.</t>
-  </si>
-  <si>
     <t>pmo</t>
   </si>
   <si>
@@ -107,18 +95,12 @@
     <t>outs_ore_mese</t>
   </si>
   <si>
-    <t>pbx_all_project_mapped_power_bi_column_set</t>
-  </si>
-  <si>
     <t>pbx_key</t>
   </si>
   <si>
     <t>pbx_pv_total</t>
   </si>
   <si>
-    <t>pbx_timesheet_information_by_month</t>
-  </si>
-  <si>
     <t>pv_date</t>
   </si>
   <si>
@@ -146,33 +128,12 @@
     <t>Caricamento Support Tables.</t>
   </si>
   <si>
-    <t>Aggiornamento tabella progetti.</t>
-  </si>
-  <si>
-    <t>Aggiornamento tabella ore lavorate X work.</t>
-  </si>
-  <si>
     <t>Aggiornamento tabella ore lavorate X work outsourcing.</t>
   </si>
   <si>
-    <t>Aggiornamento Tabella RES10.</t>
-  </si>
-  <si>
-    <t>Aggiornamento tabella approvazione Timesheet.</t>
-  </si>
-  <si>
-    <t>Chiave di selezione per PBI.</t>
-  </si>
-  <si>
-    <t>Vista PBI tabella progetti.</t>
-  </si>
-  <si>
     <t>Vista PBI tabella RES10.</t>
   </si>
   <si>
-    <t>Vista PBI tabella approvazione Timesheet.</t>
-  </si>
-  <si>
     <t>Tabella Date X update mensile.</t>
   </si>
   <si>
@@ -180,6 +141,36 @@
   </si>
   <si>
     <t>Chiave di selezione.</t>
+  </si>
+  <si>
+    <t>Update mensile progetti.</t>
+  </si>
+  <si>
+    <t>Update mensile ore lavorate X work.</t>
+  </si>
+  <si>
+    <t>Update mensile RES10.</t>
+  </si>
+  <si>
+    <t>Update mensile approvazione Timesheet.</t>
+  </si>
+  <si>
+    <t>Tabella progetti.</t>
+  </si>
+  <si>
+    <t>Tabella ore lavorate X work.</t>
+  </si>
+  <si>
+    <t>Tabella ore lavorate X work outsourcing.</t>
+  </si>
+  <si>
+    <t>Tabella chiave di selezione per PBI.</t>
+  </si>
+  <si>
+    <t>Tabella RES10.</t>
+  </si>
+  <si>
+    <t>Tabella approvazione Timesheet.</t>
   </si>
 </sst>
 </file>
@@ -551,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38693624-A12C-4727-914E-A749365BF12D}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50.28515625" customWidth="1"/>
@@ -578,7 +569,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -589,7 +580,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -600,7 +591,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -611,7 +602,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -660,13 +651,13 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -674,21 +665,21 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -696,51 +687,51 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>42</v>
@@ -748,148 +739,135 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
         <v>29</v>
-      </c>
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K0000FF Datalogic INTERNAL</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{4dae1a65-cb87-4081-a080-424f2bd6a496}" enabled="1" method="Standard" siteId="{fa92fa5a-de6c-4caf-a2ae-f13cb9d1c40a}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>